--- a/df_followers.xlsx
+++ b/df_followers.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lapto\OneDrive\Pulpit\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lapto\OneDrive\Pulpit\Scraper Social Media\Social Media Scraper 2025\temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C7546D8-A490-40DF-B560-F7FBAF42B68D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E11001F-DE43-4048-A2BF-4139222B228D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,6 +22,9 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="113">
   <si>
+    <t>Pismo</t>
+  </si>
+  <si>
     <t>Facebook</t>
   </si>
   <si>
@@ -40,6 +43,9 @@
     <t>X</t>
   </si>
   <si>
+    <t xml:space="preserve">YouTube </t>
+  </si>
+  <si>
     <t>Suma</t>
   </si>
   <si>
@@ -353,12 +359,6 @@
   </si>
   <si>
     <t>Olivia</t>
-  </si>
-  <si>
-    <t>Tytuł</t>
-  </si>
-  <si>
-    <t>YouTube</t>
   </si>
 </sst>
 </file>
@@ -737,36 +737,36 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>112</v>
+        <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B2" s="2">
         <v>768000</v>
@@ -795,7 +795,7 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B3" s="2">
         <v>1500000</v>
@@ -824,7 +824,7 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4" s="2">
         <v>824000</v>
@@ -853,7 +853,7 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B5" s="2">
         <v>957000</v>
@@ -882,7 +882,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B6" s="2">
         <v>524000</v>
@@ -911,7 +911,7 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B7" s="2">
         <v>532000</v>
@@ -940,7 +940,7 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B8" s="2">
         <v>196000</v>
@@ -969,7 +969,7 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B9" s="2">
         <v>516000</v>
@@ -998,7 +998,7 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B10" s="2">
         <v>212000</v>
@@ -1027,7 +1027,7 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B11" s="2">
         <v>596000</v>
@@ -1056,7 +1056,7 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B12" s="2">
         <v>312000</v>
@@ -1085,7 +1085,7 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B13" s="2">
         <v>330000</v>
@@ -1114,7 +1114,7 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B14" s="2">
         <v>290000</v>
@@ -1143,7 +1143,7 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B15" s="2">
         <v>328000</v>
@@ -1172,7 +1172,7 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B16" s="2">
         <v>226000</v>
@@ -1201,7 +1201,7 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B17" s="2">
         <v>358000</v>
@@ -1230,7 +1230,7 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B18" s="2">
         <v>131000</v>
@@ -1259,7 +1259,7 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B19" s="2">
         <v>43000</v>
@@ -1288,7 +1288,7 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B20" s="2">
         <v>329000</v>
@@ -1317,7 +1317,7 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B21" s="2">
         <v>157000</v>
@@ -1346,7 +1346,7 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B22" s="2">
         <v>254000</v>
@@ -1375,7 +1375,7 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B23" s="2">
         <v>124000</v>
@@ -1404,7 +1404,7 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B24" s="2">
         <v>250000</v>
@@ -1433,7 +1433,7 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B25" s="2">
         <v>113000</v>
@@ -1462,7 +1462,7 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B26" s="2">
         <v>200000</v>
@@ -1491,7 +1491,7 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B27" s="2">
         <v>157000</v>
@@ -1520,7 +1520,7 @@
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B28" s="2">
         <v>194000</v>
@@ -1549,7 +1549,7 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B29" s="2">
         <v>189000</v>
@@ -1578,7 +1578,7 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B30" s="2">
         <v>192000</v>
@@ -1607,7 +1607,7 @@
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B31" s="2">
         <v>189000</v>
@@ -1636,7 +1636,7 @@
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B32" s="2">
         <v>177000</v>
@@ -1665,7 +1665,7 @@
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B33" s="2">
         <v>162000</v>
@@ -1694,7 +1694,7 @@
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B34" s="2">
         <v>136000</v>
@@ -1723,7 +1723,7 @@
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B35" s="2">
         <v>153000</v>
@@ -1752,7 +1752,7 @@
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B36" s="2">
         <v>151000</v>
@@ -1781,7 +1781,7 @@
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B37" s="2">
         <v>65000</v>
@@ -1810,7 +1810,7 @@
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B38" s="2">
         <v>157000</v>
@@ -1839,7 +1839,7 @@
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B39" s="2">
         <v>24000</v>
@@ -1868,7 +1868,7 @@
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B40" s="2">
         <v>125000</v>
@@ -1897,7 +1897,7 @@
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B41" s="2">
         <v>145000</v>
@@ -1926,7 +1926,7 @@
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B42" s="2">
         <v>102000</v>
@@ -1955,7 +1955,7 @@
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B43" s="2">
         <v>49000</v>
@@ -1984,7 +1984,7 @@
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B44" s="2">
         <v>105000</v>
@@ -2013,7 +2013,7 @@
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B45" s="2">
         <v>39000</v>
@@ -2042,7 +2042,7 @@
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B46" s="2">
         <v>102000</v>
@@ -2071,7 +2071,7 @@
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B47" s="2">
         <v>44000</v>
@@ -2100,7 +2100,7 @@
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B48" s="2">
         <v>89000</v>
@@ -2129,7 +2129,7 @@
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B49" s="2">
         <v>80000</v>
@@ -2158,7 +2158,7 @@
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B50" s="2">
         <v>80000</v>
@@ -2187,7 +2187,7 @@
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B51" s="2">
         <v>82000</v>
@@ -2216,7 +2216,7 @@
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B52" s="2">
         <v>79000</v>
@@ -2245,7 +2245,7 @@
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B53" s="2">
         <v>80000</v>
@@ -2274,7 +2274,7 @@
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B54" s="2">
         <v>37000</v>
@@ -2303,7 +2303,7 @@
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B55" s="2">
         <v>35000</v>
@@ -2332,7 +2332,7 @@
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B56" s="2">
         <v>54000</v>
@@ -2361,7 +2361,7 @@
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B57" s="2">
         <v>22000</v>
@@ -2390,7 +2390,7 @@
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B58" s="2">
         <v>52000</v>
@@ -2419,7 +2419,7 @@
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B59" s="2">
         <v>45000</v>
@@ -2448,7 +2448,7 @@
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B60" s="2">
         <v>37000</v>
@@ -2477,7 +2477,7 @@
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B61" s="2">
         <v>43000</v>
@@ -2506,7 +2506,7 @@
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B62" s="2">
         <v>39000</v>
@@ -2535,7 +2535,7 @@
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B63" s="2">
         <v>40000</v>
@@ -2564,7 +2564,7 @@
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B64" s="2">
         <v>35000</v>
@@ -2593,7 +2593,7 @@
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B65" s="2">
         <v>37000</v>
@@ -2622,7 +2622,7 @@
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B66" s="2">
         <v>32000</v>
@@ -2651,7 +2651,7 @@
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B67" s="2">
         <v>35000</v>
@@ -2680,7 +2680,7 @@
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B68" s="2">
         <v>22000</v>
@@ -2709,7 +2709,7 @@
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B69" s="2">
         <v>31000</v>
@@ -2738,7 +2738,7 @@
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B70" s="2">
         <v>26000</v>
@@ -2767,7 +2767,7 @@
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B71" s="2">
         <v>28000</v>
@@ -2796,7 +2796,7 @@
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B72" s="2">
         <v>31000</v>
@@ -2825,7 +2825,7 @@
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B73" s="2">
         <v>28000</v>
@@ -2854,7 +2854,7 @@
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B74" s="2">
         <v>28000</v>
@@ -2883,7 +2883,7 @@
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B75" s="2">
         <v>25000</v>
@@ -2912,7 +2912,7 @@
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B76" s="2">
         <v>26000</v>
@@ -2941,7 +2941,7 @@
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B77" s="2">
         <v>25000</v>
@@ -2970,7 +2970,7 @@
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B78" s="2">
         <v>22000</v>
@@ -2999,7 +2999,7 @@
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B79" s="2">
         <v>22000</v>
@@ -3028,7 +3028,7 @@
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B80" s="2">
         <v>15000</v>
@@ -3057,7 +3057,7 @@
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B81" s="2">
         <v>0</v>
@@ -3086,7 +3086,7 @@
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B82" s="2">
         <v>8100</v>
@@ -3115,7 +3115,7 @@
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B83" s="2">
         <v>9800</v>
@@ -3144,7 +3144,7 @@
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B84" s="2">
         <v>3000</v>
@@ -3173,7 +3173,7 @@
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B85" s="2">
         <v>4200</v>
@@ -3202,7 +3202,7 @@
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B86" s="2">
         <v>9700</v>
@@ -3231,7 +3231,7 @@
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B87" s="2">
         <v>9800</v>
@@ -3260,7 +3260,7 @@
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B88" s="2">
         <v>6900</v>
@@ -3289,7 +3289,7 @@
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B89" s="2">
         <v>8000</v>
@@ -3318,7 +3318,7 @@
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B90" s="2">
         <v>7800</v>
@@ -3347,7 +3347,7 @@
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B91" s="2">
         <v>7000</v>
@@ -3376,7 +3376,7 @@
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B92" s="2">
         <v>6300</v>
@@ -3405,7 +3405,7 @@
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B93" s="2">
         <v>0</v>
@@ -3434,7 +3434,7 @@
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B94" s="2">
         <v>5900</v>
@@ -3463,7 +3463,7 @@
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B95" s="2">
         <v>5800</v>
@@ -3492,7 +3492,7 @@
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B96" s="2">
         <v>1400</v>
@@ -3521,7 +3521,7 @@
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B97" s="2">
         <v>3500</v>
@@ -3550,7 +3550,7 @@
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B98" s="2">
         <v>2100</v>
@@ -3579,7 +3579,7 @@
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B99" s="2">
         <v>2400</v>
@@ -3608,7 +3608,7 @@
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B100" s="2">
         <v>2500</v>
@@ -3637,7 +3637,7 @@
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B101" s="2">
         <v>2300</v>
@@ -3666,7 +3666,7 @@
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B102" s="2">
         <v>2200</v>
@@ -3695,7 +3695,7 @@
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B103" s="2">
         <v>2100</v>
@@ -3724,7 +3724,7 @@
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B104" s="2">
         <v>1500</v>
@@ -3753,7 +3753,7 @@
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B105" s="2">
         <v>1000</v>

--- a/df_followers.xlsx
+++ b/df_followers.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lapto\OneDrive\Pulpit\Scraper Social Media\Social Media Scraper 2025\temp\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lapto\OneDrive\Pulpit\Scraper Social Media\Pobieranie 04.2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E11001F-DE43-4048-A2BF-4139222B228D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54C43B5E-E70F-4245-AF68-7459AA73DA57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,9 +22,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="113">
   <si>
-    <t>Pismo</t>
-  </si>
-  <si>
     <t>Facebook</t>
   </si>
   <si>
@@ -359,6 +356,9 @@
   </si>
   <si>
     <t>Olivia</t>
+  </si>
+  <si>
+    <t>Tytuł</t>
   </si>
 </sst>
 </file>
@@ -737,36 +737,36 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B2" s="2">
         <v>768000</v>
@@ -795,7 +795,7 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B3" s="2">
         <v>1500000</v>
@@ -824,7 +824,7 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B4" s="2">
         <v>824000</v>
@@ -853,7 +853,7 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B5" s="2">
         <v>957000</v>
@@ -882,7 +882,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B6" s="2">
         <v>524000</v>
@@ -911,7 +911,7 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B7" s="2">
         <v>532000</v>
@@ -940,7 +940,7 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B8" s="2">
         <v>196000</v>
@@ -969,7 +969,7 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B9" s="2">
         <v>516000</v>
@@ -998,7 +998,7 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B10" s="2">
         <v>212000</v>
@@ -1027,7 +1027,7 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B11" s="2">
         <v>596000</v>
@@ -1056,7 +1056,7 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B12" s="2">
         <v>312000</v>
@@ -1085,7 +1085,7 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B13" s="2">
         <v>330000</v>
@@ -1114,7 +1114,7 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B14" s="2">
         <v>290000</v>
@@ -1143,7 +1143,7 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B15" s="2">
         <v>328000</v>
@@ -1172,7 +1172,7 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B16" s="2">
         <v>226000</v>
@@ -1201,7 +1201,7 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B17" s="2">
         <v>358000</v>
@@ -1230,7 +1230,7 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B18" s="2">
         <v>131000</v>
@@ -1259,7 +1259,7 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B19" s="2">
         <v>43000</v>
@@ -1288,7 +1288,7 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B20" s="2">
         <v>329000</v>
@@ -1317,7 +1317,7 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B21" s="2">
         <v>157000</v>
@@ -1346,7 +1346,7 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B22" s="2">
         <v>254000</v>
@@ -1375,7 +1375,7 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B23" s="2">
         <v>124000</v>
@@ -1404,7 +1404,7 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B24" s="2">
         <v>250000</v>
@@ -1433,7 +1433,7 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B25" s="2">
         <v>113000</v>
@@ -1462,7 +1462,7 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B26" s="2">
         <v>200000</v>
@@ -1491,7 +1491,7 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B27" s="2">
         <v>157000</v>
@@ -1520,7 +1520,7 @@
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B28" s="2">
         <v>194000</v>
@@ -1549,7 +1549,7 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B29" s="2">
         <v>189000</v>
@@ -1578,7 +1578,7 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B30" s="2">
         <v>192000</v>
@@ -1607,7 +1607,7 @@
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B31" s="2">
         <v>189000</v>
@@ -1636,7 +1636,7 @@
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B32" s="2">
         <v>177000</v>
@@ -1665,7 +1665,7 @@
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B33" s="2">
         <v>162000</v>
@@ -1694,7 +1694,7 @@
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B34" s="2">
         <v>136000</v>
@@ -1723,7 +1723,7 @@
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B35" s="2">
         <v>153000</v>
@@ -1752,7 +1752,7 @@
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B36" s="2">
         <v>151000</v>
@@ -1781,7 +1781,7 @@
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B37" s="2">
         <v>65000</v>
@@ -1810,7 +1810,7 @@
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B38" s="2">
         <v>157000</v>
@@ -1839,7 +1839,7 @@
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B39" s="2">
         <v>24000</v>
@@ -1868,7 +1868,7 @@
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B40" s="2">
         <v>125000</v>
@@ -1897,7 +1897,7 @@
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B41" s="2">
         <v>145000</v>
@@ -1926,7 +1926,7 @@
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B42" s="2">
         <v>102000</v>
@@ -1955,7 +1955,7 @@
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B43" s="2">
         <v>49000</v>
@@ -1984,7 +1984,7 @@
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B44" s="2">
         <v>105000</v>
@@ -2013,7 +2013,7 @@
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B45" s="2">
         <v>39000</v>
@@ -2042,7 +2042,7 @@
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B46" s="2">
         <v>102000</v>
@@ -2071,7 +2071,7 @@
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B47" s="2">
         <v>44000</v>
@@ -2100,7 +2100,7 @@
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B48" s="2">
         <v>89000</v>
@@ -2129,7 +2129,7 @@
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B49" s="2">
         <v>80000</v>
@@ -2158,7 +2158,7 @@
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B50" s="2">
         <v>80000</v>
@@ -2187,7 +2187,7 @@
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B51" s="2">
         <v>82000</v>
@@ -2216,7 +2216,7 @@
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B52" s="2">
         <v>79000</v>
@@ -2245,7 +2245,7 @@
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B53" s="2">
         <v>80000</v>
@@ -2274,7 +2274,7 @@
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B54" s="2">
         <v>37000</v>
@@ -2303,7 +2303,7 @@
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B55" s="2">
         <v>35000</v>
@@ -2332,7 +2332,7 @@
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B56" s="2">
         <v>54000</v>
@@ -2361,7 +2361,7 @@
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B57" s="2">
         <v>22000</v>
@@ -2390,7 +2390,7 @@
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B58" s="2">
         <v>52000</v>
@@ -2419,7 +2419,7 @@
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B59" s="2">
         <v>45000</v>
@@ -2448,7 +2448,7 @@
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B60" s="2">
         <v>37000</v>
@@ -2477,7 +2477,7 @@
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B61" s="2">
         <v>43000</v>
@@ -2506,7 +2506,7 @@
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B62" s="2">
         <v>39000</v>
@@ -2535,7 +2535,7 @@
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B63" s="2">
         <v>40000</v>
@@ -2564,7 +2564,7 @@
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B64" s="2">
         <v>35000</v>
@@ -2593,7 +2593,7 @@
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B65" s="2">
         <v>37000</v>
@@ -2622,7 +2622,7 @@
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B66" s="2">
         <v>32000</v>
@@ -2651,7 +2651,7 @@
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B67" s="2">
         <v>35000</v>
@@ -2680,7 +2680,7 @@
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B68" s="2">
         <v>22000</v>
@@ -2709,7 +2709,7 @@
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B69" s="2">
         <v>31000</v>
@@ -2738,7 +2738,7 @@
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B70" s="2">
         <v>26000</v>
@@ -2767,7 +2767,7 @@
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B71" s="2">
         <v>28000</v>
@@ -2796,7 +2796,7 @@
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B72" s="2">
         <v>31000</v>
@@ -2825,7 +2825,7 @@
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B73" s="2">
         <v>28000</v>
@@ -2854,7 +2854,7 @@
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B74" s="2">
         <v>28000</v>
@@ -2883,7 +2883,7 @@
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B75" s="2">
         <v>25000</v>
@@ -2912,7 +2912,7 @@
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B76" s="2">
         <v>26000</v>
@@ -2941,7 +2941,7 @@
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B77" s="2">
         <v>25000</v>
@@ -2970,7 +2970,7 @@
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B78" s="2">
         <v>22000</v>
@@ -2999,7 +2999,7 @@
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B79" s="2">
         <v>22000</v>
@@ -3028,7 +3028,7 @@
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B80" s="2">
         <v>15000</v>
@@ -3057,7 +3057,7 @@
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B81" s="2">
         <v>0</v>
@@ -3086,7 +3086,7 @@
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B82" s="2">
         <v>8100</v>
@@ -3115,7 +3115,7 @@
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B83" s="2">
         <v>9800</v>
@@ -3144,7 +3144,7 @@
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B84" s="2">
         <v>3000</v>
@@ -3173,7 +3173,7 @@
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B85" s="2">
         <v>4200</v>
@@ -3202,7 +3202,7 @@
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B86" s="2">
         <v>9700</v>
@@ -3231,7 +3231,7 @@
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B87" s="2">
         <v>9800</v>
@@ -3260,7 +3260,7 @@
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B88" s="2">
         <v>6900</v>
@@ -3289,7 +3289,7 @@
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B89" s="2">
         <v>8000</v>
@@ -3318,7 +3318,7 @@
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B90" s="2">
         <v>7800</v>
@@ -3347,7 +3347,7 @@
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B91" s="2">
         <v>7000</v>
@@ -3376,7 +3376,7 @@
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B92" s="2">
         <v>6300</v>
@@ -3405,7 +3405,7 @@
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B93" s="2">
         <v>0</v>
@@ -3434,7 +3434,7 @@
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B94" s="2">
         <v>5900</v>
@@ -3463,7 +3463,7 @@
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B95" s="2">
         <v>5800</v>
@@ -3492,7 +3492,7 @@
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B96" s="2">
         <v>1400</v>
@@ -3521,7 +3521,7 @@
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B97" s="2">
         <v>3500</v>
@@ -3550,7 +3550,7 @@
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B98" s="2">
         <v>2100</v>
@@ -3579,7 +3579,7 @@
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B99" s="2">
         <v>2400</v>
@@ -3608,7 +3608,7 @@
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B100" s="2">
         <v>2500</v>
@@ -3637,7 +3637,7 @@
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B101" s="2">
         <v>2300</v>
@@ -3666,7 +3666,7 @@
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B102" s="2">
         <v>2200</v>
@@ -3695,7 +3695,7 @@
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B103" s="2">
         <v>2100</v>
@@ -3724,7 +3724,7 @@
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B104" s="2">
         <v>1500</v>
@@ -3753,7 +3753,7 @@
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B105" s="2">
         <v>1000</v>

--- a/df_followers.xlsx
+++ b/df_followers.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lapto\OneDrive\Pulpit\Scraper Social Media\Pobieranie 04.2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54C43B5E-E70F-4245-AF68-7459AA73DA57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{553FB3DE-BA51-4016-84A4-FEAC8C4B7446}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,9 +40,6 @@
     <t>X</t>
   </si>
   <si>
-    <t xml:space="preserve">YouTube </t>
-  </si>
-  <si>
     <t>Suma</t>
   </si>
   <si>
@@ -359,6 +356,9 @@
   </si>
   <si>
     <t>Tytuł</t>
+  </si>
+  <si>
+    <t>YouTube</t>
   </si>
 </sst>
 </file>
@@ -737,7 +737,7 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -758,15 +758,15 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B2" s="2">
         <v>768000</v>
@@ -795,7 +795,7 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B3" s="2">
         <v>1500000</v>
@@ -824,7 +824,7 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B4" s="2">
         <v>824000</v>
@@ -853,7 +853,7 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B5" s="2">
         <v>957000</v>
@@ -882,7 +882,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B6" s="2">
         <v>524000</v>
@@ -911,7 +911,7 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B7" s="2">
         <v>532000</v>
@@ -940,7 +940,7 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B8" s="2">
         <v>196000</v>
@@ -969,7 +969,7 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B9" s="2">
         <v>516000</v>
@@ -998,7 +998,7 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B10" s="2">
         <v>212000</v>
@@ -1027,7 +1027,7 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B11" s="2">
         <v>596000</v>
@@ -1056,7 +1056,7 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B12" s="2">
         <v>312000</v>
@@ -1085,7 +1085,7 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B13" s="2">
         <v>330000</v>
@@ -1114,7 +1114,7 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B14" s="2">
         <v>290000</v>
@@ -1143,7 +1143,7 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B15" s="2">
         <v>328000</v>
@@ -1172,7 +1172,7 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B16" s="2">
         <v>226000</v>
@@ -1201,7 +1201,7 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B17" s="2">
         <v>358000</v>
@@ -1230,7 +1230,7 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B18" s="2">
         <v>131000</v>
@@ -1259,7 +1259,7 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B19" s="2">
         <v>43000</v>
@@ -1288,7 +1288,7 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B20" s="2">
         <v>329000</v>
@@ -1317,7 +1317,7 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B21" s="2">
         <v>157000</v>
@@ -1346,7 +1346,7 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B22" s="2">
         <v>254000</v>
@@ -1375,7 +1375,7 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B23" s="2">
         <v>124000</v>
@@ -1404,7 +1404,7 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B24" s="2">
         <v>250000</v>
@@ -1433,7 +1433,7 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B25" s="2">
         <v>113000</v>
@@ -1462,7 +1462,7 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B26" s="2">
         <v>200000</v>
@@ -1491,7 +1491,7 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B27" s="2">
         <v>157000</v>
@@ -1520,7 +1520,7 @@
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B28" s="2">
         <v>194000</v>
@@ -1549,7 +1549,7 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B29" s="2">
         <v>189000</v>
@@ -1578,7 +1578,7 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B30" s="2">
         <v>192000</v>
@@ -1607,7 +1607,7 @@
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B31" s="2">
         <v>189000</v>
@@ -1636,7 +1636,7 @@
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B32" s="2">
         <v>177000</v>
@@ -1665,7 +1665,7 @@
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B33" s="2">
         <v>162000</v>
@@ -1694,7 +1694,7 @@
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B34" s="2">
         <v>136000</v>
@@ -1723,7 +1723,7 @@
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B35" s="2">
         <v>153000</v>
@@ -1752,7 +1752,7 @@
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B36" s="2">
         <v>151000</v>
@@ -1781,7 +1781,7 @@
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B37" s="2">
         <v>65000</v>
@@ -1810,7 +1810,7 @@
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B38" s="2">
         <v>157000</v>
@@ -1839,7 +1839,7 @@
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B39" s="2">
         <v>24000</v>
@@ -1868,7 +1868,7 @@
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B40" s="2">
         <v>125000</v>
@@ -1897,7 +1897,7 @@
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B41" s="2">
         <v>145000</v>
@@ -1926,7 +1926,7 @@
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B42" s="2">
         <v>102000</v>
@@ -1955,7 +1955,7 @@
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B43" s="2">
         <v>49000</v>
@@ -1984,7 +1984,7 @@
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B44" s="2">
         <v>105000</v>
@@ -2013,7 +2013,7 @@
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B45" s="2">
         <v>39000</v>
@@ -2042,7 +2042,7 @@
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B46" s="2">
         <v>102000</v>
@@ -2071,7 +2071,7 @@
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B47" s="2">
         <v>44000</v>
@@ -2100,7 +2100,7 @@
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B48" s="2">
         <v>89000</v>
@@ -2129,7 +2129,7 @@
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B49" s="2">
         <v>80000</v>
@@ -2158,7 +2158,7 @@
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B50" s="2">
         <v>80000</v>
@@ -2187,7 +2187,7 @@
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B51" s="2">
         <v>82000</v>
@@ -2216,7 +2216,7 @@
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B52" s="2">
         <v>79000</v>
@@ -2245,7 +2245,7 @@
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B53" s="2">
         <v>80000</v>
@@ -2274,7 +2274,7 @@
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B54" s="2">
         <v>37000</v>
@@ -2303,7 +2303,7 @@
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B55" s="2">
         <v>35000</v>
@@ -2332,7 +2332,7 @@
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B56" s="2">
         <v>54000</v>
@@ -2361,7 +2361,7 @@
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B57" s="2">
         <v>22000</v>
@@ -2390,7 +2390,7 @@
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B58" s="2">
         <v>52000</v>
@@ -2419,7 +2419,7 @@
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B59" s="2">
         <v>45000</v>
@@ -2448,7 +2448,7 @@
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B60" s="2">
         <v>37000</v>
@@ -2477,7 +2477,7 @@
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B61" s="2">
         <v>43000</v>
@@ -2506,7 +2506,7 @@
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B62" s="2">
         <v>39000</v>
@@ -2535,7 +2535,7 @@
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B63" s="2">
         <v>40000</v>
@@ -2564,7 +2564,7 @@
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B64" s="2">
         <v>35000</v>
@@ -2593,7 +2593,7 @@
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B65" s="2">
         <v>37000</v>
@@ -2622,7 +2622,7 @@
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B66" s="2">
         <v>32000</v>
@@ -2651,7 +2651,7 @@
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B67" s="2">
         <v>35000</v>
@@ -2680,7 +2680,7 @@
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B68" s="2">
         <v>22000</v>
@@ -2709,7 +2709,7 @@
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B69" s="2">
         <v>31000</v>
@@ -2738,7 +2738,7 @@
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B70" s="2">
         <v>26000</v>
@@ -2767,7 +2767,7 @@
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B71" s="2">
         <v>28000</v>
@@ -2796,7 +2796,7 @@
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B72" s="2">
         <v>31000</v>
@@ -2825,7 +2825,7 @@
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B73" s="2">
         <v>28000</v>
@@ -2854,7 +2854,7 @@
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B74" s="2">
         <v>28000</v>
@@ -2883,7 +2883,7 @@
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B75" s="2">
         <v>25000</v>
@@ -2912,7 +2912,7 @@
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B76" s="2">
         <v>26000</v>
@@ -2941,7 +2941,7 @@
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B77" s="2">
         <v>25000</v>
@@ -2970,7 +2970,7 @@
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B78" s="2">
         <v>22000</v>
@@ -2999,7 +2999,7 @@
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B79" s="2">
         <v>22000</v>
@@ -3028,7 +3028,7 @@
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B80" s="2">
         <v>15000</v>
@@ -3057,7 +3057,7 @@
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B81" s="2">
         <v>0</v>
@@ -3086,7 +3086,7 @@
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B82" s="2">
         <v>8100</v>
@@ -3115,7 +3115,7 @@
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B83" s="2">
         <v>9800</v>
@@ -3144,7 +3144,7 @@
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B84" s="2">
         <v>3000</v>
@@ -3173,7 +3173,7 @@
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B85" s="2">
         <v>4200</v>
@@ -3202,7 +3202,7 @@
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B86" s="2">
         <v>9700</v>
@@ -3231,7 +3231,7 @@
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B87" s="2">
         <v>9800</v>
@@ -3260,7 +3260,7 @@
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B88" s="2">
         <v>6900</v>
@@ -3289,7 +3289,7 @@
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B89" s="2">
         <v>8000</v>
@@ -3318,7 +3318,7 @@
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B90" s="2">
         <v>7800</v>
@@ -3347,7 +3347,7 @@
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B91" s="2">
         <v>7000</v>
@@ -3376,7 +3376,7 @@
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B92" s="2">
         <v>6300</v>
@@ -3405,7 +3405,7 @@
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B93" s="2">
         <v>0</v>
@@ -3434,7 +3434,7 @@
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B94" s="2">
         <v>5900</v>
@@ -3463,7 +3463,7 @@
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B95" s="2">
         <v>5800</v>
@@ -3492,7 +3492,7 @@
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B96" s="2">
         <v>1400</v>
@@ -3521,7 +3521,7 @@
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B97" s="2">
         <v>3500</v>
@@ -3550,7 +3550,7 @@
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B98" s="2">
         <v>2100</v>
@@ -3579,7 +3579,7 @@
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B99" s="2">
         <v>2400</v>
@@ -3608,7 +3608,7 @@
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B100" s="2">
         <v>2500</v>
@@ -3637,7 +3637,7 @@
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B101" s="2">
         <v>2300</v>
@@ -3666,7 +3666,7 @@
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B102" s="2">
         <v>2200</v>
@@ -3695,7 +3695,7 @@
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B103" s="2">
         <v>2100</v>
@@ -3724,7 +3724,7 @@
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B104" s="2">
         <v>1500</v>
@@ -3753,7 +3753,7 @@
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B105" s="2">
         <v>1000</v>

--- a/df_followers.xlsx
+++ b/df_followers.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lapto\OneDrive\Pulpit\Scraper Social Media\Pobieranie 04.2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{553FB3DE-BA51-4016-84A4-FEAC8C4B7446}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3388A6B1-812D-45B9-BB66-00C5D889A655}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,6 +22,9 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="113">
   <si>
+    <t>Tytuł</t>
+  </si>
+  <si>
     <t>Facebook</t>
   </si>
   <si>
@@ -40,6 +43,9 @@
     <t>X</t>
   </si>
   <si>
+    <t>YouTube</t>
+  </si>
+  <si>
     <t>Suma</t>
   </si>
   <si>
@@ -100,12 +106,12 @@
     <t>National Geographic Traveler</t>
   </si>
   <si>
+    <t>Dziennik Zachodni</t>
+  </si>
+  <si>
     <t>Tygodnik Powszechny</t>
   </si>
   <si>
-    <t>Dziennik Zachodni</t>
-  </si>
-  <si>
     <t>Murator</t>
   </si>
   <si>
@@ -124,12 +130,12 @@
     <t>Nowiny</t>
   </si>
   <si>
+    <t>Głos Wielkopolski</t>
+  </si>
+  <si>
     <t>Echo Dnia</t>
   </si>
   <si>
-    <t>Głos Wielkopolski</t>
-  </si>
-  <si>
     <t>Gazeta Pomorska</t>
   </si>
   <si>
@@ -142,33 +148,33 @@
     <t>Gazeta Olsztyńska Tygodnik</t>
   </si>
   <si>
+    <t>Dziennik Bałtycki</t>
+  </si>
+  <si>
     <t>Gazeta Lubuska</t>
   </si>
   <si>
-    <t>Dziennik Bałtycki</t>
+    <t>Tygodnik Poradnik Rolniczy</t>
   </si>
   <si>
     <t>Elle Decoration</t>
   </si>
   <si>
+    <t>Dziennik Gazeta Prawna</t>
+  </si>
+  <si>
     <t>Cztery Kąty</t>
   </si>
   <si>
-    <t>Dziennik Gazeta Prawna</t>
-  </si>
-  <si>
-    <t>Tygodnik Poradnik Rolniczy</t>
-  </si>
-  <si>
     <t>Nowa Trybuna Opolska</t>
   </si>
   <si>
+    <t>Wieści Rolnicze</t>
+  </si>
+  <si>
     <t>Weranda</t>
   </si>
   <si>
-    <t>Wieści Rolnicze</t>
-  </si>
-  <si>
     <t>Kurier Poranny</t>
   </si>
   <si>
@@ -178,18 +184,21 @@
     <t>Express Ilustrowany</t>
   </si>
   <si>
+    <t>Express Bydgoski</t>
+  </si>
+  <si>
+    <t>Dziennik Łódzki</t>
+  </si>
+  <si>
     <t>Parkiet Gazeta Giełdy</t>
   </si>
   <si>
-    <t>Express Bydgoski</t>
-  </si>
-  <si>
-    <t>Dziennik Łódzki</t>
-  </si>
-  <si>
     <t>Głos - Dziennik Pomorza</t>
   </si>
   <si>
+    <t>Twój Styl</t>
+  </si>
+  <si>
     <t>SENS</t>
   </si>
   <si>
@@ -202,7 +211,7 @@
     <t>Weranda Country</t>
   </si>
   <si>
-    <t>Twój Styl</t>
+    <t>Polska Metropolia Warszawska</t>
   </si>
   <si>
     <t>Kurier Szczeciński</t>
@@ -211,51 +220,48 @@
     <t>Wysokie Obcasy Extra</t>
   </si>
   <si>
-    <t>Polska Metropolia Warszawska</t>
-  </si>
-  <si>
     <t>Dziennik Polski</t>
   </si>
   <si>
     <t>Pani</t>
   </si>
   <si>
+    <t>Gazeta Współczesna</t>
+  </si>
+  <si>
     <t>Ładny Dom</t>
   </si>
   <si>
-    <t>Gazeta Współczesna</t>
+    <t>Tele Tydzień</t>
   </si>
   <si>
     <t>Świat Wiedzy</t>
   </si>
   <si>
-    <t>Tele Tydzień</t>
-  </si>
-  <si>
     <t>Świat Seriali</t>
   </si>
   <si>
     <t>Świerszczyk</t>
   </si>
   <si>
+    <t>Wiadomości Rolnicze Polska</t>
+  </si>
+  <si>
     <t>DOZ Magazyn Dbam o Zdrowie</t>
   </si>
   <si>
-    <t>Wiadomości Rolnicze Polska</t>
-  </si>
-  <si>
     <t>Dziennik Elbląski Tygodnik</t>
   </si>
   <si>
+    <t>Newsweek Polska Historia</t>
+  </si>
+  <si>
     <t>Tygodnik Angora</t>
   </si>
   <si>
     <t>Automobilista</t>
   </si>
   <si>
-    <t>Newsweek Polska Historia</t>
-  </si>
-  <si>
     <t>Wiedza i Życie</t>
   </si>
   <si>
@@ -280,21 +286,21 @@
     <t>Przegląd</t>
   </si>
   <si>
+    <t>Ogólnopolskie Pismo Rynku FMCG Hurt &amp; Detal</t>
+  </si>
+  <si>
     <t>Gazeta Olsztyńska / Dziennik Elbląski</t>
   </si>
   <si>
     <t>Szef Kuchni Magazyn Branży Gastronomicznej</t>
   </si>
   <si>
+    <t>Miesięcznik Dealer</t>
+  </si>
+  <si>
     <t>Zawód:Architekt</t>
   </si>
   <si>
-    <t>Ogólnopolskie Pismo Rynku FMCG Hurt &amp; Detal</t>
-  </si>
-  <si>
-    <t>Miesięcznik Dealer</t>
-  </si>
-  <si>
     <t>Poradnik Restauratora</t>
   </si>
   <si>
@@ -313,12 +319,12 @@
     <t>Teraz Wilanów</t>
   </si>
   <si>
+    <t>Poradnik Handlowca</t>
+  </si>
+  <si>
     <t>Ekspert Budowlany</t>
   </si>
   <si>
-    <t>Poradnik Handlowca</t>
-  </si>
-  <si>
     <t>Mały Gość Niedzielny</t>
   </si>
   <si>
@@ -353,19 +359,13 @@
   </si>
   <si>
     <t>Olivia</t>
-  </si>
-  <si>
-    <t>Tytuł</t>
-  </si>
-  <si>
-    <t>YouTube</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -379,6 +379,15 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -417,12 +426,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normalny" xfId="0" builtinId="0"/>
@@ -730,49 +748,49 @@
   <dimension ref="A1:I105"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="23.90625" customWidth="1"/>
-    <col min="2" max="8" width="10.6328125" customWidth="1"/>
-    <col min="9" max="9" width="10.36328125" customWidth="1"/>
+    <col min="1" max="1" width="28.6328125" customWidth="1"/>
+    <col min="2" max="8" width="15.6328125" customWidth="1"/>
+    <col min="9" max="9" width="21" style="5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B2" s="2">
-        <v>768000</v>
+        <v>833000</v>
       </c>
       <c r="C2" s="2">
-        <v>58800</v>
+        <v>67800</v>
       </c>
       <c r="D2" s="2">
         <v>0</v>
@@ -781,27 +799,27 @@
         <v>0</v>
       </c>
       <c r="F2" s="2">
-        <v>319300</v>
+        <v>344300</v>
       </c>
       <c r="G2" s="2">
-        <v>33900</v>
+        <v>34800</v>
       </c>
       <c r="H2" s="2">
-        <v>1240000</v>
-      </c>
-      <c r="I2" s="2">
-        <v>2420000</v>
+        <v>1260000</v>
+      </c>
+      <c r="I2" s="4">
+        <v>2539900</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B3" s="2">
-        <v>1500000</v>
+        <v>1600000</v>
       </c>
       <c r="C3" s="2">
-        <v>83700</v>
+        <v>89200</v>
       </c>
       <c r="D3" s="2">
         <v>0</v>
@@ -810,56 +828,56 @@
         <v>0</v>
       </c>
       <c r="F3" s="2">
-        <v>264600</v>
+        <v>283500</v>
       </c>
       <c r="G3" s="2">
-        <v>65500</v>
+        <v>66000</v>
       </c>
       <c r="H3" s="2">
-        <v>399000</v>
-      </c>
-      <c r="I3" s="2">
-        <v>2312800</v>
+        <v>406000</v>
+      </c>
+      <c r="I3" s="4">
+        <v>2444700</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4" s="2">
-        <v>824000</v>
+        <v>831000</v>
       </c>
       <c r="C4" s="2">
-        <v>206000</v>
+        <v>208000</v>
       </c>
       <c r="D4" s="2">
-        <v>18370</v>
+        <v>18455</v>
       </c>
       <c r="E4" s="2">
         <v>0</v>
       </c>
       <c r="F4" s="2">
-        <v>39700</v>
+        <v>43000</v>
       </c>
       <c r="G4" s="2">
-        <v>731000</v>
+        <v>728600</v>
       </c>
       <c r="H4" s="2">
-        <v>30400</v>
-      </c>
-      <c r="I4" s="2">
-        <v>1849470</v>
+        <v>38700</v>
+      </c>
+      <c r="I4" s="4">
+        <v>1867755</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B5" s="2">
-        <v>957000</v>
+        <v>972000</v>
       </c>
       <c r="C5" s="2">
-        <v>83400</v>
+        <v>87200</v>
       </c>
       <c r="D5" s="2">
         <v>0</v>
@@ -868,33 +886,33 @@
         <v>0</v>
       </c>
       <c r="F5" s="2">
-        <v>99300</v>
+        <v>109800</v>
       </c>
       <c r="G5" s="2">
-        <v>268300</v>
+        <v>268800</v>
       </c>
       <c r="H5" s="2">
-        <v>306000</v>
-      </c>
-      <c r="I5" s="2">
-        <v>1714000</v>
+        <v>299000</v>
+      </c>
+      <c r="I5" s="4">
+        <v>1736800</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B6" s="2">
-        <v>524000</v>
+        <v>540000</v>
       </c>
       <c r="C6" s="2">
-        <v>139000</v>
+        <v>141000</v>
       </c>
       <c r="D6" s="2">
         <v>0</v>
       </c>
       <c r="E6" s="2">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F6" s="2">
         <v>0</v>
@@ -903,44 +921,44 @@
         <v>0</v>
       </c>
       <c r="H6" s="2">
-        <v>866000</v>
-      </c>
-      <c r="I6" s="2">
-        <v>1529043</v>
+        <v>884000</v>
+      </c>
+      <c r="I6" s="4">
+        <v>1565042</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B7" s="2">
-        <v>532000</v>
+        <v>534000</v>
       </c>
       <c r="C7" s="2">
-        <v>66100</v>
+        <v>66900</v>
       </c>
       <c r="D7" s="2">
         <v>0</v>
       </c>
       <c r="E7" s="2">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="F7" s="2">
         <v>0</v>
       </c>
       <c r="G7" s="2">
-        <v>797200</v>
+        <v>796200</v>
       </c>
       <c r="H7" s="2">
-        <v>28600</v>
-      </c>
-      <c r="I7" s="2">
-        <v>1424710</v>
+        <v>29700</v>
+      </c>
+      <c r="I7" s="4">
+        <v>1427611</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B8" s="2">
         <v>196000</v>
@@ -958,24 +976,24 @@
         <v>0</v>
       </c>
       <c r="G8" s="2">
-        <v>86700</v>
+        <v>86800</v>
       </c>
       <c r="H8" s="2">
-        <v>515000</v>
-      </c>
-      <c r="I8" s="2">
-        <v>797700</v>
+        <v>530000</v>
+      </c>
+      <c r="I8" s="4">
+        <v>812800</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B9" s="2">
-        <v>516000</v>
+        <v>533000</v>
       </c>
       <c r="C9" s="2">
-        <v>107000</v>
+        <v>112000</v>
       </c>
       <c r="D9" s="2">
         <v>0</v>
@@ -984,56 +1002,56 @@
         <v>0</v>
       </c>
       <c r="F9" s="2">
-        <v>22400</v>
+        <v>24900</v>
       </c>
       <c r="G9" s="2">
         <v>0</v>
       </c>
       <c r="H9" s="2">
-        <v>100000</v>
-      </c>
-      <c r="I9" s="2">
-        <v>745400</v>
+        <v>108000</v>
+      </c>
+      <c r="I9" s="4">
+        <v>777900</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B10" s="2">
-        <v>212000</v>
+        <v>222000</v>
       </c>
       <c r="C10" s="2">
-        <v>25800</v>
+        <v>26700</v>
       </c>
       <c r="D10" s="2">
-        <v>36900</v>
+        <v>38245</v>
       </c>
       <c r="E10" s="2">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="F10" s="2">
         <v>0</v>
       </c>
       <c r="G10" s="2">
-        <v>356700</v>
+        <v>358500</v>
       </c>
       <c r="H10" s="2">
-        <v>104000</v>
-      </c>
-      <c r="I10" s="2">
-        <v>736067</v>
+        <v>107000</v>
+      </c>
+      <c r="I10" s="4">
+        <v>753111</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B11" s="2">
-        <v>596000</v>
+        <v>597000</v>
       </c>
       <c r="C11" s="2">
-        <v>26600</v>
+        <v>26400</v>
       </c>
       <c r="D11" s="2">
         <v>0</v>
@@ -1042,27 +1060,27 @@
         <v>0</v>
       </c>
       <c r="F11" s="2">
-        <v>4928</v>
+        <v>4937</v>
       </c>
       <c r="G11" s="2">
         <v>0</v>
       </c>
       <c r="H11" s="2">
-        <v>97500</v>
-      </c>
-      <c r="I11" s="2">
-        <v>725028</v>
+        <v>97900</v>
+      </c>
+      <c r="I11" s="4">
+        <v>726237</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B12" s="2">
-        <v>312000</v>
+        <v>318000</v>
       </c>
       <c r="C12" s="2">
-        <v>176000</v>
+        <v>189000</v>
       </c>
       <c r="D12" s="2">
         <v>0</v>
@@ -1071,30 +1089,30 @@
         <v>979</v>
       </c>
       <c r="F12" s="2">
-        <v>145500</v>
+        <v>157900</v>
       </c>
       <c r="G12" s="2">
         <v>0</v>
       </c>
       <c r="H12" s="2">
-        <v>41200</v>
-      </c>
-      <c r="I12" s="2">
-        <v>675679</v>
+        <v>41800</v>
+      </c>
+      <c r="I12" s="4">
+        <v>707679</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B13" s="2">
-        <v>330000</v>
+        <v>335000</v>
       </c>
       <c r="C13" s="2">
-        <v>52000</v>
+        <v>54100</v>
       </c>
       <c r="D13" s="2">
-        <v>12446</v>
+        <v>12600</v>
       </c>
       <c r="E13" s="2">
         <v>0</v>
@@ -1103,53 +1121,53 @@
         <v>0</v>
       </c>
       <c r="G13" s="2">
-        <v>225400</v>
+        <v>225300</v>
       </c>
       <c r="H13" s="2">
-        <v>20300</v>
-      </c>
-      <c r="I13" s="2">
-        <v>640146</v>
+        <v>26200</v>
+      </c>
+      <c r="I13" s="4">
+        <v>653200</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B14" s="2">
-        <v>290000</v>
+        <v>294000</v>
       </c>
       <c r="C14" s="2">
-        <v>37300</v>
+        <v>41100</v>
       </c>
       <c r="D14" s="2">
-        <v>229668</v>
+        <v>235591</v>
       </c>
       <c r="E14" s="2">
         <v>0</v>
       </c>
       <c r="F14" s="2">
-        <v>756</v>
+        <v>762</v>
       </c>
       <c r="G14" s="2">
-        <v>48500</v>
+        <v>48700</v>
       </c>
       <c r="H14" s="2">
         <v>0</v>
       </c>
-      <c r="I14" s="2">
-        <v>606224</v>
+      <c r="I14" s="4">
+        <v>620153</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B15" s="2">
-        <v>328000</v>
+        <v>340000</v>
       </c>
       <c r="C15" s="2">
-        <v>131000</v>
+        <v>132000</v>
       </c>
       <c r="D15" s="2">
         <v>0</v>
@@ -1158,27 +1176,27 @@
         <v>0</v>
       </c>
       <c r="F15" s="2">
-        <v>36400</v>
+        <v>39900</v>
       </c>
       <c r="G15" s="2">
         <v>0</v>
       </c>
       <c r="H15" s="2">
-        <v>58800</v>
-      </c>
-      <c r="I15" s="2">
-        <v>554200</v>
+        <v>63100</v>
+      </c>
+      <c r="I15" s="4">
+        <v>575000</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B16" s="2">
-        <v>226000</v>
+        <v>232000</v>
       </c>
       <c r="C16" s="2">
-        <v>178000</v>
+        <v>187000</v>
       </c>
       <c r="D16" s="2">
         <v>0</v>
@@ -1187,27 +1205,27 @@
         <v>92</v>
       </c>
       <c r="F16" s="2">
-        <v>86400</v>
+        <v>92900</v>
       </c>
       <c r="G16" s="2">
         <v>0</v>
       </c>
       <c r="H16" s="2">
-        <v>18500</v>
-      </c>
-      <c r="I16" s="2">
-        <v>508992</v>
+        <v>20500</v>
+      </c>
+      <c r="I16" s="4">
+        <v>532492</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B17" s="2">
-        <v>358000</v>
+        <v>360000</v>
       </c>
       <c r="C17" s="2">
-        <v>136000</v>
+        <v>138000</v>
       </c>
       <c r="D17" s="2">
         <v>0</v>
@@ -1222,24 +1240,24 @@
         <v>0</v>
       </c>
       <c r="H17" s="2">
-        <v>6960</v>
-      </c>
-      <c r="I17" s="2">
-        <v>500960</v>
+        <v>7000</v>
+      </c>
+      <c r="I17" s="4">
+        <v>505000</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B18" s="2">
-        <v>131000</v>
+        <v>134000</v>
       </c>
       <c r="C18" s="2">
-        <v>7759</v>
+        <v>8057</v>
       </c>
       <c r="D18" s="2">
-        <v>122880</v>
+        <v>125961</v>
       </c>
       <c r="E18" s="2">
         <v>0</v>
@@ -1248,24 +1266,24 @@
         <v>0</v>
       </c>
       <c r="G18" s="2">
-        <v>70500</v>
+        <v>70900</v>
       </c>
       <c r="H18" s="2">
-        <v>10100</v>
-      </c>
-      <c r="I18" s="2">
-        <v>342239</v>
+        <v>11600</v>
+      </c>
+      <c r="I18" s="4">
+        <v>350518</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B19" s="2">
-        <v>43000</v>
+        <v>44000</v>
       </c>
       <c r="C19" s="2">
-        <v>3947</v>
+        <v>3939</v>
       </c>
       <c r="D19" s="2">
         <v>0</v>
@@ -1277,21 +1295,21 @@
         <v>0</v>
       </c>
       <c r="G19" s="2">
-        <v>170900</v>
+        <v>171900</v>
       </c>
       <c r="H19" s="2">
-        <v>120000</v>
-      </c>
-      <c r="I19" s="2">
-        <v>337847</v>
+        <v>127000</v>
+      </c>
+      <c r="I19" s="4">
+        <v>346839</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B20" s="2">
-        <v>329000</v>
+        <v>333000</v>
       </c>
       <c r="C20" s="2">
         <v>0</v>
@@ -1311,77 +1329,77 @@
       <c r="H20" s="2">
         <v>0</v>
       </c>
-      <c r="I20" s="2">
-        <v>329000</v>
+      <c r="I20" s="4">
+        <v>333000</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B21" s="2">
-        <v>157000</v>
+        <v>269000</v>
       </c>
       <c r="C21" s="2">
-        <v>54900</v>
+        <v>3670</v>
       </c>
       <c r="D21" s="2">
-        <v>1570</v>
+        <v>634</v>
       </c>
       <c r="E21" s="2">
         <v>0</v>
       </c>
       <c r="F21" s="2">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="G21" s="2">
-        <v>60800</v>
+        <v>11400</v>
       </c>
       <c r="H21" s="2">
-        <v>13400</v>
-      </c>
-      <c r="I21" s="2">
-        <v>287670</v>
+        <v>8820</v>
+      </c>
+      <c r="I21" s="4">
+        <v>293578</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B22" s="2">
-        <v>254000</v>
+        <v>161000</v>
       </c>
       <c r="C22" s="2">
-        <v>3504</v>
+        <v>56100</v>
       </c>
       <c r="D22" s="2">
-        <v>618</v>
+        <v>1663</v>
       </c>
       <c r="E22" s="2">
         <v>0</v>
       </c>
       <c r="F22" s="2">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="G22" s="2">
-        <v>11300</v>
+        <v>60900</v>
       </c>
       <c r="H22" s="2">
-        <v>8700</v>
-      </c>
-      <c r="I22" s="2">
-        <v>278168</v>
+        <v>13800</v>
+      </c>
+      <c r="I22" s="4">
+        <v>293463</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B23" s="2">
-        <v>124000</v>
+        <v>135000</v>
       </c>
       <c r="C23" s="2">
-        <v>9222</v>
+        <v>9328</v>
       </c>
       <c r="D23" s="2">
         <v>0</v>
@@ -1390,27 +1408,27 @@
         <v>29700</v>
       </c>
       <c r="F23" s="2">
-        <v>20000</v>
+        <v>23800</v>
       </c>
       <c r="G23" s="2">
         <v>0</v>
       </c>
       <c r="H23" s="2">
-        <v>82200</v>
-      </c>
-      <c r="I23" s="2">
-        <v>265122</v>
+        <v>82400</v>
+      </c>
+      <c r="I23" s="4">
+        <v>280228</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B24" s="2">
-        <v>250000</v>
+        <v>255000</v>
       </c>
       <c r="C24" s="2">
-        <v>1695</v>
+        <v>1864</v>
       </c>
       <c r="D24" s="2">
         <v>65</v>
@@ -1422,53 +1440,53 @@
         <v>0</v>
       </c>
       <c r="G24" s="2">
-        <v>545</v>
+        <v>559</v>
       </c>
       <c r="H24" s="2">
-        <v>1750</v>
-      </c>
-      <c r="I24" s="2">
-        <v>254055</v>
+        <v>1760</v>
+      </c>
+      <c r="I24" s="4">
+        <v>259248</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B25" s="2">
-        <v>113000</v>
+        <v>120000</v>
       </c>
       <c r="C25" s="2">
-        <v>21400</v>
+        <v>21700</v>
       </c>
       <c r="D25" s="2">
-        <v>813</v>
+        <v>863</v>
       </c>
       <c r="E25" s="2">
         <v>0</v>
       </c>
       <c r="F25" s="2">
-        <v>27600</v>
+        <v>29000</v>
       </c>
       <c r="G25" s="2">
-        <v>4933</v>
+        <v>4966</v>
       </c>
       <c r="H25" s="2">
-        <v>65900</v>
-      </c>
-      <c r="I25" s="2">
-        <v>233646</v>
+        <v>66300</v>
+      </c>
+      <c r="I25" s="4">
+        <v>242829</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B26" s="2">
-        <v>200000</v>
+        <v>206000</v>
       </c>
       <c r="C26" s="2">
-        <v>3371</v>
+        <v>3478</v>
       </c>
       <c r="D26" s="2">
         <v>0</v>
@@ -1480,18 +1498,18 @@
         <v>0</v>
       </c>
       <c r="G26" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H26" s="2">
-        <v>21800</v>
-      </c>
-      <c r="I26" s="2">
-        <v>225339</v>
+        <v>22200</v>
+      </c>
+      <c r="I26" s="4">
+        <v>231845</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B27" s="2">
         <v>157000</v>
@@ -1509,27 +1527,27 @@
         <v>0</v>
       </c>
       <c r="G27" s="2">
-        <v>38800</v>
+        <v>39100</v>
       </c>
       <c r="H27" s="2">
-        <v>14600</v>
-      </c>
-      <c r="I27" s="2">
-        <v>221900</v>
+        <v>15000</v>
+      </c>
+      <c r="I27" s="4">
+        <v>222600</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B28" s="2">
-        <v>194000</v>
+        <v>197000</v>
       </c>
       <c r="C28" s="2">
-        <v>3054</v>
+        <v>3102</v>
       </c>
       <c r="D28" s="2">
-        <v>477</v>
+        <v>513</v>
       </c>
       <c r="E28" s="2">
         <v>0</v>
@@ -1538,27 +1556,27 @@
         <v>0</v>
       </c>
       <c r="G28" s="2">
-        <v>3144</v>
+        <v>3172</v>
       </c>
       <c r="H28" s="2">
-        <v>11800</v>
-      </c>
-      <c r="I28" s="2">
-        <v>212475</v>
+        <v>11900</v>
+      </c>
+      <c r="I28" s="4">
+        <v>215687</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B29" s="2">
-        <v>189000</v>
+        <v>200000</v>
       </c>
       <c r="C29" s="2">
-        <v>2138</v>
+        <v>6691</v>
       </c>
       <c r="D29" s="2">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="E29" s="2">
         <v>0</v>
@@ -1567,27 +1585,27 @@
         <v>0</v>
       </c>
       <c r="G29" s="2">
-        <v>1285</v>
+        <v>6636</v>
       </c>
       <c r="H29" s="2">
-        <v>13300</v>
-      </c>
-      <c r="I29" s="2">
-        <v>205762</v>
+        <v>691</v>
+      </c>
+      <c r="I29" s="4">
+        <v>214018</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B30" s="2">
-        <v>192000</v>
+        <v>193000</v>
       </c>
       <c r="C30" s="2">
-        <v>5976</v>
+        <v>2290</v>
       </c>
       <c r="D30" s="2">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="E30" s="2">
         <v>0</v>
@@ -1596,24 +1614,24 @@
         <v>0</v>
       </c>
       <c r="G30" s="2">
-        <v>6642</v>
+        <v>1277</v>
       </c>
       <c r="H30" s="2">
-        <v>620</v>
-      </c>
-      <c r="I30" s="2">
-        <v>205238</v>
+        <v>13300</v>
+      </c>
+      <c r="I30" s="4">
+        <v>209909</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B31" s="2">
-        <v>189000</v>
+        <v>194000</v>
       </c>
       <c r="C31" s="2">
-        <v>2430</v>
+        <v>2516</v>
       </c>
       <c r="D31" s="2">
         <v>0</v>
@@ -1625,56 +1643,56 @@
         <v>0</v>
       </c>
       <c r="G31" s="2">
-        <v>5326</v>
+        <v>5360</v>
       </c>
       <c r="H31" s="2">
-        <v>3990</v>
-      </c>
-      <c r="I31" s="2">
-        <v>200746</v>
+        <v>4010</v>
+      </c>
+      <c r="I31" s="4">
+        <v>205886</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B32" s="2">
-        <v>177000</v>
+        <v>181000</v>
       </c>
       <c r="C32" s="2">
-        <v>2984</v>
+        <v>3077</v>
       </c>
       <c r="D32" s="2">
         <v>0</v>
       </c>
       <c r="E32" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F32" s="2">
         <v>0</v>
       </c>
       <c r="G32" s="2">
-        <v>12700</v>
+        <v>12800</v>
       </c>
       <c r="H32" s="2">
-        <v>4190</v>
-      </c>
-      <c r="I32" s="2">
-        <v>197027</v>
+        <v>4570</v>
+      </c>
+      <c r="I32" s="4">
+        <v>201599</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B33" s="2">
-        <v>162000</v>
+        <v>169000</v>
       </c>
       <c r="C33" s="2">
-        <v>10200</v>
+        <v>10300</v>
       </c>
       <c r="D33" s="2">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="E33" s="2">
         <v>0</v>
@@ -1686,21 +1704,21 @@
         <v>5448</v>
       </c>
       <c r="H33" s="2">
-        <v>357</v>
-      </c>
-      <c r="I33" s="2">
-        <v>178046</v>
+        <v>382</v>
+      </c>
+      <c r="I33" s="4">
+        <v>185179</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B34" s="2">
-        <v>136000</v>
+        <v>142000</v>
       </c>
       <c r="C34" s="2">
-        <v>7651</v>
+        <v>7730</v>
       </c>
       <c r="D34" s="2">
         <v>0</v>
@@ -1709,120 +1727,120 @@
         <v>0</v>
       </c>
       <c r="F34" s="2">
-        <v>3148</v>
+        <v>3130</v>
       </c>
       <c r="G34" s="2">
-        <v>4253</v>
+        <v>4232</v>
       </c>
       <c r="H34" s="2">
-        <v>20400</v>
-      </c>
-      <c r="I34" s="2">
-        <v>171452</v>
+        <v>27000</v>
+      </c>
+      <c r="I34" s="4">
+        <v>184092</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B35" s="2">
-        <v>153000</v>
+        <v>158000</v>
       </c>
       <c r="C35" s="2">
-        <v>4871</v>
+        <v>8318</v>
       </c>
       <c r="D35" s="2">
-        <v>175</v>
+        <v>86</v>
       </c>
       <c r="E35" s="2">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="F35" s="2">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G35" s="2">
-        <v>3337</v>
+        <v>8787</v>
       </c>
       <c r="H35" s="2">
-        <v>9360</v>
-      </c>
-      <c r="I35" s="2">
-        <v>170791</v>
+        <v>2190</v>
+      </c>
+      <c r="I35" s="4">
+        <v>177409</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B36" s="2">
-        <v>151000</v>
+        <v>158000</v>
       </c>
       <c r="C36" s="2">
-        <v>7799</v>
+        <v>4946</v>
       </c>
       <c r="D36" s="2">
-        <v>85</v>
+        <v>191</v>
       </c>
       <c r="E36" s="2">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="F36" s="2">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="G36" s="2">
-        <v>8747</v>
+        <v>3354</v>
       </c>
       <c r="H36" s="2">
-        <v>778</v>
-      </c>
-      <c r="I36" s="2">
-        <v>168433</v>
+        <v>9390</v>
+      </c>
+      <c r="I36" s="4">
+        <v>175929</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B37" s="2">
-        <v>65000</v>
+        <v>137000</v>
       </c>
       <c r="C37" s="2">
-        <v>55300</v>
+        <v>9162</v>
       </c>
       <c r="D37" s="2">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="E37" s="2">
-        <v>166</v>
+        <v>0</v>
       </c>
       <c r="F37" s="2">
         <v>0</v>
       </c>
       <c r="G37" s="2">
-        <v>0</v>
+        <v>1843</v>
       </c>
       <c r="H37" s="2">
-        <v>41200</v>
-      </c>
-      <c r="I37" s="2">
-        <v>161666</v>
+        <v>20600</v>
+      </c>
+      <c r="I37" s="4">
+        <v>168749</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B38" s="2">
-        <v>157000</v>
+        <v>67000</v>
       </c>
       <c r="C38" s="2">
-        <v>2724</v>
+        <v>57700</v>
       </c>
       <c r="D38" s="2">
         <v>0</v>
       </c>
       <c r="E38" s="2">
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="F38" s="2">
         <v>0</v>
@@ -1831,24 +1849,24 @@
         <v>0</v>
       </c>
       <c r="H38" s="2">
-        <v>0</v>
-      </c>
-      <c r="I38" s="2">
-        <v>159724</v>
+        <v>41800</v>
+      </c>
+      <c r="I38" s="4">
+        <v>166668</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B39" s="2">
-        <v>24000</v>
+        <v>25000</v>
       </c>
       <c r="C39" s="2">
-        <v>4700</v>
+        <v>5430</v>
       </c>
       <c r="D39" s="2">
-        <v>61769</v>
+        <v>62491</v>
       </c>
       <c r="E39" s="2">
         <v>0</v>
@@ -1857,27 +1875,27 @@
         <v>0</v>
       </c>
       <c r="G39" s="2">
-        <v>45300</v>
+        <v>45700</v>
       </c>
       <c r="H39" s="2">
-        <v>20800</v>
-      </c>
-      <c r="I39" s="2">
-        <v>156569</v>
+        <v>22800</v>
+      </c>
+      <c r="I39" s="4">
+        <v>161421</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B40" s="2">
-        <v>125000</v>
+        <v>157000</v>
       </c>
       <c r="C40" s="2">
-        <v>9124</v>
+        <v>2742</v>
       </c>
       <c r="D40" s="2">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="E40" s="2">
         <v>0</v>
@@ -1886,27 +1904,27 @@
         <v>0</v>
       </c>
       <c r="G40" s="2">
-        <v>1852</v>
+        <v>0</v>
       </c>
       <c r="H40" s="2">
-        <v>19200</v>
-      </c>
-      <c r="I40" s="2">
-        <v>155316</v>
+        <v>0</v>
+      </c>
+      <c r="I40" s="4">
+        <v>159742</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B41" s="2">
-        <v>145000</v>
+        <v>148000</v>
       </c>
       <c r="C41" s="2">
         <v>0</v>
       </c>
       <c r="D41" s="2">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="E41" s="2">
         <v>0</v>
@@ -1915,82 +1933,82 @@
         <v>0</v>
       </c>
       <c r="G41" s="2">
-        <v>3381</v>
+        <v>3370</v>
       </c>
       <c r="H41" s="2">
-        <v>6560</v>
-      </c>
-      <c r="I41" s="2">
-        <v>155099</v>
+        <v>6710</v>
+      </c>
+      <c r="I41" s="4">
+        <v>158247</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B42" s="2">
-        <v>102000</v>
+        <v>68000</v>
       </c>
       <c r="C42" s="2">
-        <v>42400</v>
+        <v>1852</v>
       </c>
       <c r="D42" s="2">
         <v>0</v>
       </c>
       <c r="E42" s="2">
-        <v>1300</v>
+        <v>0</v>
       </c>
       <c r="F42" s="2">
-        <v>0</v>
+        <v>12200</v>
       </c>
       <c r="G42" s="2">
         <v>0</v>
       </c>
       <c r="H42" s="2">
-        <v>0</v>
-      </c>
-      <c r="I42" s="2">
-        <v>145700</v>
+        <v>72300</v>
+      </c>
+      <c r="I42" s="4">
+        <v>154352</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B43" s="2">
-        <v>49000</v>
+        <v>104000</v>
       </c>
       <c r="C43" s="2">
-        <v>1777</v>
+        <v>43600</v>
       </c>
       <c r="D43" s="2">
         <v>0</v>
       </c>
       <c r="E43" s="2">
-        <v>0</v>
+        <v>1300</v>
       </c>
       <c r="F43" s="2">
-        <v>11200</v>
+        <v>0</v>
       </c>
       <c r="G43" s="2">
         <v>0</v>
       </c>
       <c r="H43" s="2">
-        <v>70300</v>
-      </c>
-      <c r="I43" s="2">
-        <v>132277</v>
+        <v>0</v>
+      </c>
+      <c r="I43" s="4">
+        <v>148900</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B44" s="2">
-        <v>105000</v>
+        <v>107000</v>
       </c>
       <c r="C44" s="2">
-        <v>4149</v>
+        <v>4167</v>
       </c>
       <c r="D44" s="2">
         <v>0</v>
@@ -2002,24 +2020,24 @@
         <v>0</v>
       </c>
       <c r="G44" s="2">
-        <v>3234</v>
+        <v>3239</v>
       </c>
       <c r="H44" s="2">
         <v>4240</v>
       </c>
-      <c r="I44" s="2">
-        <v>116623</v>
+      <c r="I44" s="4">
+        <v>118646</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B45" s="2">
         <v>39000</v>
       </c>
       <c r="C45" s="2">
-        <v>7537</v>
+        <v>7570</v>
       </c>
       <c r="D45" s="2">
         <v>0</v>
@@ -2031,24 +2049,24 @@
         <v>0</v>
       </c>
       <c r="G45" s="2">
-        <v>28700</v>
+        <v>28800</v>
       </c>
       <c r="H45" s="2">
-        <v>40100</v>
-      </c>
-      <c r="I45" s="2">
-        <v>115337</v>
+        <v>40200</v>
+      </c>
+      <c r="I45" s="4">
+        <v>115570</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B46" s="2">
-        <v>102000</v>
+        <v>105000</v>
       </c>
       <c r="C46" s="2">
-        <v>3073</v>
+        <v>3100</v>
       </c>
       <c r="D46" s="2">
         <v>0</v>
@@ -2060,21 +2078,21 @@
         <v>0</v>
       </c>
       <c r="G46" s="2">
-        <v>1385</v>
+        <v>1381</v>
       </c>
       <c r="H46" s="2">
         <v>2550</v>
       </c>
-      <c r="I46" s="2">
-        <v>109008</v>
+      <c r="I46" s="4">
+        <v>112031</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B47" s="2">
-        <v>44000</v>
+        <v>94000</v>
       </c>
       <c r="C47" s="2">
         <v>0</v>
@@ -2089,27 +2107,27 @@
         <v>0</v>
       </c>
       <c r="G47" s="2">
-        <v>28000</v>
+        <v>3130</v>
       </c>
       <c r="H47" s="2">
-        <v>23300</v>
-      </c>
-      <c r="I47" s="2">
-        <v>95300</v>
+        <v>2810</v>
+      </c>
+      <c r="I47" s="4">
+        <v>99940</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B48" s="2">
-        <v>89000</v>
+        <v>84000</v>
       </c>
       <c r="C48" s="2">
-        <v>0</v>
+        <v>3060</v>
       </c>
       <c r="D48" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E48" s="2">
         <v>0</v>
@@ -2118,27 +2136,27 @@
         <v>0</v>
       </c>
       <c r="G48" s="2">
-        <v>3096</v>
+        <v>4471</v>
       </c>
       <c r="H48" s="2">
-        <v>2800</v>
-      </c>
-      <c r="I48" s="2">
-        <v>94896</v>
+        <v>4810</v>
+      </c>
+      <c r="I48" s="4">
+        <v>96343</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B49" s="2">
-        <v>80000</v>
+        <v>44000</v>
       </c>
       <c r="C49" s="2">
-        <v>2974</v>
+        <v>0</v>
       </c>
       <c r="D49" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E49" s="2">
         <v>0</v>
@@ -2147,24 +2165,24 @@
         <v>0</v>
       </c>
       <c r="G49" s="2">
-        <v>4480</v>
+        <v>28300</v>
       </c>
       <c r="H49" s="2">
-        <v>4800</v>
-      </c>
-      <c r="I49" s="2">
-        <v>92256</v>
+        <v>23900</v>
+      </c>
+      <c r="I49" s="4">
+        <v>96200</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B50" s="2">
         <v>80000</v>
       </c>
       <c r="C50" s="2">
-        <v>1473</v>
+        <v>1496</v>
       </c>
       <c r="D50" s="2">
         <v>0</v>
@@ -2176,24 +2194,24 @@
         <v>0</v>
       </c>
       <c r="G50" s="2">
-        <v>1789</v>
+        <v>1782</v>
       </c>
       <c r="H50" s="2">
-        <v>6290</v>
-      </c>
-      <c r="I50" s="2">
-        <v>89552</v>
+        <v>6300</v>
+      </c>
+      <c r="I50" s="4">
+        <v>89578</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B51" s="2">
-        <v>82000</v>
+        <v>45000</v>
       </c>
       <c r="C51" s="2">
-        <v>1707</v>
+        <v>40000</v>
       </c>
       <c r="D51" s="2">
         <v>0</v>
@@ -2202,7 +2220,7 @@
         <v>0</v>
       </c>
       <c r="F51" s="2">
-        <v>0</v>
+        <v>4108</v>
       </c>
       <c r="G51" s="2">
         <v>0</v>
@@ -2210,19 +2228,19 @@
       <c r="H51" s="2">
         <v>0</v>
       </c>
-      <c r="I51" s="2">
-        <v>83707</v>
+      <c r="I51" s="4">
+        <v>89108</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B52" s="2">
-        <v>79000</v>
+        <v>84000</v>
       </c>
       <c r="C52" s="2">
-        <v>772</v>
+        <v>1773</v>
       </c>
       <c r="D52" s="2">
         <v>0</v>
@@ -2234,24 +2252,24 @@
         <v>0</v>
       </c>
       <c r="G52" s="2">
-        <v>2151</v>
+        <v>0</v>
       </c>
       <c r="H52" s="2">
-        <v>1300</v>
-      </c>
-      <c r="I52" s="2">
-        <v>83223</v>
+        <v>0</v>
+      </c>
+      <c r="I52" s="4">
+        <v>85773</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B53" s="2">
-        <v>80000</v>
+        <v>81000</v>
       </c>
       <c r="C53" s="2">
-        <v>0</v>
+        <v>816</v>
       </c>
       <c r="D53" s="2">
         <v>0</v>
@@ -2263,30 +2281,30 @@
         <v>0</v>
       </c>
       <c r="G53" s="2">
-        <v>0</v>
+        <v>2158</v>
       </c>
       <c r="H53" s="2">
-        <v>0</v>
-      </c>
-      <c r="I53" s="2">
-        <v>80000</v>
+        <v>1310</v>
+      </c>
+      <c r="I53" s="4">
+        <v>85284</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B54" s="2">
-        <v>37000</v>
+        <v>81000</v>
       </c>
       <c r="C54" s="2">
-        <v>31200</v>
+        <v>0</v>
       </c>
       <c r="D54" s="2">
         <v>0</v>
       </c>
       <c r="E54" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="F54" s="2">
         <v>0</v>
@@ -2297,28 +2315,28 @@
       <c r="H54" s="2">
         <v>0</v>
       </c>
-      <c r="I54" s="2">
-        <v>78200</v>
+      <c r="I54" s="4">
+        <v>81000</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B55" s="2">
-        <v>35000</v>
+        <v>37000</v>
       </c>
       <c r="C55" s="2">
-        <v>37800</v>
+        <v>33500</v>
       </c>
       <c r="D55" s="2">
         <v>0</v>
       </c>
       <c r="E55" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="F55" s="2">
-        <v>2169</v>
+        <v>0</v>
       </c>
       <c r="G55" s="2">
         <v>0</v>
@@ -2326,16 +2344,16 @@
       <c r="H55" s="2">
         <v>0</v>
       </c>
-      <c r="I55" s="2">
-        <v>74969</v>
+      <c r="I55" s="4">
+        <v>80500</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B56" s="2">
-        <v>54000</v>
+        <v>74000</v>
       </c>
       <c r="C56" s="2">
         <v>0</v>
@@ -2347,27 +2365,27 @@
         <v>0</v>
       </c>
       <c r="F56" s="2">
-        <v>1132</v>
+        <v>0</v>
       </c>
       <c r="G56" s="2">
-        <v>2769</v>
+        <v>0</v>
       </c>
       <c r="H56" s="2">
-        <v>3990</v>
-      </c>
-      <c r="I56" s="2">
-        <v>61891</v>
+        <v>0</v>
+      </c>
+      <c r="I56" s="4">
+        <v>74000</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B57" s="2">
-        <v>22000</v>
+        <v>57000</v>
       </c>
       <c r="C57" s="2">
-        <v>30300</v>
+        <v>0</v>
       </c>
       <c r="D57" s="2">
         <v>0</v>
@@ -2376,27 +2394,27 @@
         <v>0</v>
       </c>
       <c r="F57" s="2">
-        <v>0</v>
+        <v>1128</v>
       </c>
       <c r="G57" s="2">
-        <v>0</v>
+        <v>2764</v>
       </c>
       <c r="H57" s="2">
-        <v>0</v>
-      </c>
-      <c r="I57" s="2">
-        <v>52300</v>
+        <v>4320</v>
+      </c>
+      <c r="I57" s="4">
+        <v>65212</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B58" s="2">
-        <v>52000</v>
+        <v>22000</v>
       </c>
       <c r="C58" s="2">
-        <v>0</v>
+        <v>30100</v>
       </c>
       <c r="D58" s="2">
         <v>0</v>
@@ -2413,22 +2431,22 @@
       <c r="H58" s="2">
         <v>0</v>
       </c>
-      <c r="I58" s="2">
-        <v>52000</v>
+      <c r="I58" s="4">
+        <v>52100</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B59" s="2">
-        <v>45000</v>
+        <v>46000</v>
       </c>
       <c r="C59" s="2">
         <v>0</v>
       </c>
       <c r="D59" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E59" s="2">
         <v>0</v>
@@ -2437,24 +2455,24 @@
         <v>0</v>
       </c>
       <c r="G59" s="2">
-        <v>1929</v>
+        <v>1933</v>
       </c>
       <c r="H59" s="2">
         <v>0</v>
       </c>
-      <c r="I59" s="2">
-        <v>46961</v>
+      <c r="I59" s="4">
+        <v>47966</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B60" s="2">
-        <v>37000</v>
+        <v>40000</v>
       </c>
       <c r="C60" s="2">
-        <v>6619</v>
+        <v>6796</v>
       </c>
       <c r="D60" s="2">
         <v>0</v>
@@ -2471,19 +2489,19 @@
       <c r="H60" s="2">
         <v>0</v>
       </c>
-      <c r="I60" s="2">
-        <v>43619</v>
+      <c r="I60" s="4">
+        <v>46796</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B61" s="2">
-        <v>43000</v>
+        <v>40000</v>
       </c>
       <c r="C61" s="2">
-        <v>349</v>
+        <v>714</v>
       </c>
       <c r="D61" s="2">
         <v>0</v>
@@ -2495,24 +2513,24 @@
         <v>0</v>
       </c>
       <c r="G61" s="2">
-        <v>0</v>
+        <v>2123</v>
       </c>
       <c r="H61" s="2">
-        <v>0</v>
-      </c>
-      <c r="I61" s="2">
-        <v>43349</v>
+        <v>15</v>
+      </c>
+      <c r="I61" s="4">
+        <v>42852</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B62" s="2">
-        <v>39000</v>
+        <v>42000</v>
       </c>
       <c r="C62" s="2">
-        <v>713</v>
+        <v>371</v>
       </c>
       <c r="D62" s="2">
         <v>0</v>
@@ -2524,24 +2542,24 @@
         <v>0</v>
       </c>
       <c r="G62" s="2">
-        <v>2128</v>
+        <v>0</v>
       </c>
       <c r="H62" s="2">
-        <v>15</v>
-      </c>
-      <c r="I62" s="2">
-        <v>41856</v>
+        <v>0</v>
+      </c>
+      <c r="I62" s="4">
+        <v>42371</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B63" s="2">
-        <v>40000</v>
+        <v>36000</v>
       </c>
       <c r="C63" s="2">
-        <v>0</v>
+        <v>4783</v>
       </c>
       <c r="D63" s="2">
         <v>0</v>
@@ -2558,19 +2576,19 @@
       <c r="H63" s="2">
         <v>0</v>
       </c>
-      <c r="I63" s="2">
-        <v>40000</v>
+      <c r="I63" s="4">
+        <v>40783</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B64" s="2">
-        <v>35000</v>
+        <v>40000</v>
       </c>
       <c r="C64" s="2">
-        <v>4792</v>
+        <v>0</v>
       </c>
       <c r="D64" s="2">
         <v>0</v>
@@ -2587,19 +2605,19 @@
       <c r="H64" s="2">
         <v>0</v>
       </c>
-      <c r="I64" s="2">
-        <v>39792</v>
+      <c r="I64" s="4">
+        <v>40000</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B65" s="2">
         <v>37000</v>
       </c>
       <c r="C65" s="2">
-        <v>1018</v>
+        <v>1230</v>
       </c>
       <c r="D65" s="2">
         <v>0</v>
@@ -2616,19 +2634,19 @@
       <c r="H65" s="2">
         <v>0</v>
       </c>
-      <c r="I65" s="2">
-        <v>38018</v>
+      <c r="I65" s="4">
+        <v>38230</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B66" s="2">
-        <v>32000</v>
+        <v>33000</v>
       </c>
       <c r="C66" s="2">
-        <v>4172</v>
+        <v>4520</v>
       </c>
       <c r="D66" s="2">
         <v>0</v>
@@ -2643,21 +2661,21 @@
         <v>0</v>
       </c>
       <c r="H66" s="2">
-        <v>617</v>
-      </c>
-      <c r="I66" s="2">
-        <v>36789</v>
+        <v>632</v>
+      </c>
+      <c r="I66" s="4">
+        <v>38152</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B67" s="2">
-        <v>35000</v>
+        <v>25000</v>
       </c>
       <c r="C67" s="2">
-        <v>692</v>
+        <v>0</v>
       </c>
       <c r="D67" s="2">
         <v>0</v>
@@ -2666,27 +2684,27 @@
         <v>0</v>
       </c>
       <c r="F67" s="2">
-        <v>0</v>
+        <v>2909</v>
       </c>
       <c r="G67" s="2">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H67" s="2">
-        <v>0</v>
-      </c>
-      <c r="I67" s="2">
-        <v>35692</v>
+        <v>9360</v>
+      </c>
+      <c r="I67" s="4">
+        <v>37294</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B68" s="2">
-        <v>22000</v>
+        <v>35000</v>
       </c>
       <c r="C68" s="2">
-        <v>0</v>
+        <v>695</v>
       </c>
       <c r="D68" s="2">
         <v>0</v>
@@ -2695,24 +2713,24 @@
         <v>0</v>
       </c>
       <c r="F68" s="2">
-        <v>2179</v>
+        <v>0</v>
       </c>
       <c r="G68" s="2">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="H68" s="2">
-        <v>8710</v>
-      </c>
-      <c r="I68" s="2">
-        <v>32915</v>
+        <v>0</v>
+      </c>
+      <c r="I68" s="4">
+        <v>35695</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B69" s="2">
-        <v>31000</v>
+        <v>32000</v>
       </c>
       <c r="C69" s="2">
         <v>0</v>
@@ -2727,24 +2745,24 @@
         <v>0</v>
       </c>
       <c r="G69" s="2">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="H69" s="2">
         <v>1170</v>
       </c>
-      <c r="I69" s="2">
-        <v>32794</v>
+      <c r="I69" s="4">
+        <v>33792</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B70" s="2">
-        <v>26000</v>
+        <v>33000</v>
       </c>
       <c r="C70" s="2">
-        <v>995</v>
+        <v>0</v>
       </c>
       <c r="D70" s="2">
         <v>0</v>
@@ -2756,24 +2774,24 @@
         <v>0</v>
       </c>
       <c r="G70" s="2">
-        <v>2735</v>
+        <v>0</v>
       </c>
       <c r="H70" s="2">
-        <v>2690</v>
-      </c>
-      <c r="I70" s="2">
-        <v>32420</v>
+        <v>0</v>
+      </c>
+      <c r="I70" s="4">
+        <v>33000</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B71" s="2">
-        <v>28000</v>
+        <v>26000</v>
       </c>
       <c r="C71" s="2">
-        <v>3317</v>
+        <v>1253</v>
       </c>
       <c r="D71" s="2">
         <v>0</v>
@@ -2785,24 +2803,24 @@
         <v>0</v>
       </c>
       <c r="G71" s="2">
-        <v>0</v>
+        <v>2744</v>
       </c>
       <c r="H71" s="2">
-        <v>105</v>
-      </c>
-      <c r="I71" s="2">
-        <v>31422</v>
+        <v>2710</v>
+      </c>
+      <c r="I71" s="4">
+        <v>32707</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B72" s="2">
-        <v>31000</v>
+        <v>29000</v>
       </c>
       <c r="C72" s="2">
-        <v>0</v>
+        <v>3439</v>
       </c>
       <c r="D72" s="2">
         <v>0</v>
@@ -2817,18 +2835,18 @@
         <v>0</v>
       </c>
       <c r="H72" s="2">
-        <v>0</v>
-      </c>
-      <c r="I72" s="2">
-        <v>31000</v>
+        <v>103</v>
+      </c>
+      <c r="I72" s="4">
+        <v>32542</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B73" s="2">
-        <v>28000</v>
+        <v>29000</v>
       </c>
       <c r="C73" s="2">
         <v>0</v>
@@ -2848,16 +2866,16 @@
       <c r="H73" s="2">
         <v>0</v>
       </c>
-      <c r="I73" s="2">
-        <v>28000</v>
+      <c r="I73" s="4">
+        <v>29000</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B74" s="2">
-        <v>28000</v>
+        <v>29000</v>
       </c>
       <c r="C74" s="2">
         <v>0</v>
@@ -2877,16 +2895,16 @@
       <c r="H74" s="2">
         <v>0</v>
       </c>
-      <c r="I74" s="2">
-        <v>28000</v>
+      <c r="I74" s="4">
+        <v>29000</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B75" s="2">
-        <v>25000</v>
+        <v>26000</v>
       </c>
       <c r="C75" s="2">
         <v>0</v>
@@ -2898,24 +2916,24 @@
         <v>0</v>
       </c>
       <c r="F75" s="2">
-        <v>1880</v>
+        <v>1970</v>
       </c>
       <c r="G75" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="H75" s="2">
         <v>247</v>
       </c>
-      <c r="I75" s="2">
-        <v>27220</v>
+      <c r="I75" s="4">
+        <v>28312</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B76" s="2">
-        <v>26000</v>
+        <v>27000</v>
       </c>
       <c r="C76" s="2">
         <v>0</v>
@@ -2933,15 +2951,15 @@
         <v>0</v>
       </c>
       <c r="H76" s="2">
-        <v>549</v>
-      </c>
-      <c r="I76" s="2">
-        <v>26549</v>
+        <v>568</v>
+      </c>
+      <c r="I76" s="4">
+        <v>27568</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B77" s="2">
         <v>25000</v>
@@ -2964,16 +2982,16 @@
       <c r="H77" s="2">
         <v>0</v>
       </c>
-      <c r="I77" s="2">
+      <c r="I77" s="4">
         <v>25000</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B78" s="2">
-        <v>22000</v>
+        <v>23000</v>
       </c>
       <c r="C78" s="2">
         <v>0</v>
@@ -2991,18 +3009,18 @@
         <v>0</v>
       </c>
       <c r="H78" s="2">
-        <v>182</v>
-      </c>
-      <c r="I78" s="2">
-        <v>22228</v>
+        <v>185</v>
+      </c>
+      <c r="I78" s="4">
+        <v>23231</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B79" s="2">
-        <v>22000</v>
+        <v>23000</v>
       </c>
       <c r="C79" s="2">
         <v>0</v>
@@ -3022,13 +3040,13 @@
       <c r="H79" s="2">
         <v>0</v>
       </c>
-      <c r="I79" s="2">
-        <v>22000</v>
+      <c r="I79" s="4">
+        <v>23000</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B80" s="2">
         <v>15000</v>
@@ -3046,85 +3064,85 @@
         <v>0</v>
       </c>
       <c r="G80" s="2">
-        <v>2437</v>
+        <v>2419</v>
       </c>
       <c r="H80" s="2">
-        <v>788</v>
-      </c>
-      <c r="I80" s="2">
-        <v>18225</v>
+        <v>823</v>
+      </c>
+      <c r="I80" s="4">
+        <v>18242</v>
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B81" s="2">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="C81" s="2">
-        <v>7651</v>
+        <v>115</v>
       </c>
       <c r="D81" s="2">
-        <v>0</v>
+        <v>7051</v>
       </c>
       <c r="E81" s="2">
         <v>0</v>
       </c>
       <c r="F81" s="2">
-        <v>3148</v>
+        <v>0</v>
       </c>
       <c r="G81" s="2">
-        <v>4253</v>
+        <v>0</v>
       </c>
       <c r="H81" s="2">
-        <v>0</v>
-      </c>
-      <c r="I81" s="2">
-        <v>15052</v>
+        <v>5090</v>
+      </c>
+      <c r="I81" s="4">
+        <v>15256</v>
       </c>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B82" s="2">
-        <v>8100</v>
+        <v>0</v>
       </c>
       <c r="C82" s="2">
-        <v>4447</v>
+        <v>7730</v>
       </c>
       <c r="D82" s="2">
-        <v>894</v>
+        <v>0</v>
       </c>
       <c r="E82" s="2">
         <v>0</v>
       </c>
       <c r="F82" s="2">
-        <v>0</v>
+        <v>3130</v>
       </c>
       <c r="G82" s="2">
-        <v>0</v>
+        <v>4232</v>
       </c>
       <c r="H82" s="2">
         <v>0</v>
       </c>
-      <c r="I82" s="2">
-        <v>13441</v>
+      <c r="I82" s="4">
+        <v>15092</v>
       </c>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B83" s="2">
-        <v>9800</v>
+        <v>8400</v>
       </c>
       <c r="C83" s="2">
-        <v>3001</v>
+        <v>4617</v>
       </c>
       <c r="D83" s="2">
-        <v>0</v>
+        <v>916</v>
       </c>
       <c r="E83" s="2">
         <v>0</v>
@@ -3138,22 +3156,22 @@
       <c r="H83" s="2">
         <v>0</v>
       </c>
-      <c r="I83" s="2">
-        <v>12801</v>
+      <c r="I83" s="4">
+        <v>13933</v>
       </c>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B84" s="2">
-        <v>3000</v>
+        <v>4400</v>
       </c>
       <c r="C84" s="2">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="D84" s="2">
-        <v>6746</v>
+        <v>8518</v>
       </c>
       <c r="E84" s="2">
         <v>0</v>
@@ -3165,24 +3183,24 @@
         <v>0</v>
       </c>
       <c r="H84" s="2">
-        <v>2760</v>
-      </c>
-      <c r="I84" s="2">
-        <v>12615</v>
+        <v>80</v>
+      </c>
+      <c r="I84" s="4">
+        <v>12998</v>
       </c>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B85" s="2">
-        <v>4200</v>
+        <v>9800</v>
       </c>
       <c r="C85" s="2">
-        <v>0</v>
+        <v>2989</v>
       </c>
       <c r="D85" s="2">
-        <v>8264</v>
+        <v>0</v>
       </c>
       <c r="E85" s="2">
         <v>0</v>
@@ -3194,18 +3212,18 @@
         <v>0</v>
       </c>
       <c r="H85" s="2">
-        <v>79</v>
-      </c>
-      <c r="I85" s="2">
-        <v>12543</v>
+        <v>0</v>
+      </c>
+      <c r="I85" s="4">
+        <v>12789</v>
       </c>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B86" s="2">
-        <v>9700</v>
+        <v>10000</v>
       </c>
       <c r="C86" s="2">
         <v>1526</v>
@@ -3225,13 +3243,13 @@
       <c r="H86" s="2">
         <v>0</v>
       </c>
-      <c r="I86" s="2">
-        <v>11226</v>
+      <c r="I86" s="4">
+        <v>11526</v>
       </c>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B87" s="2">
         <v>9800</v>
@@ -3254,19 +3272,19 @@
       <c r="H87" s="2">
         <v>0</v>
       </c>
-      <c r="I87" s="2">
+      <c r="I87" s="4">
         <v>10800</v>
       </c>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B88" s="2">
         <v>6900</v>
       </c>
       <c r="C88" s="2">
-        <v>1642</v>
+        <v>1659</v>
       </c>
       <c r="D88" s="2">
         <v>0</v>
@@ -3278,53 +3296,53 @@
         <v>0</v>
       </c>
       <c r="G88" s="2">
-        <v>927</v>
+        <v>932</v>
       </c>
       <c r="H88" s="2">
-        <v>1170</v>
-      </c>
-      <c r="I88" s="2">
-        <v>10639</v>
+        <v>1180</v>
+      </c>
+      <c r="I88" s="4">
+        <v>10671</v>
       </c>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B89" s="2">
-        <v>8000</v>
+        <v>8100</v>
       </c>
       <c r="C89" s="2">
         <v>0</v>
       </c>
       <c r="D89" s="2">
-        <v>657</v>
+        <v>667</v>
       </c>
       <c r="E89" s="2">
         <v>0</v>
       </c>
       <c r="F89" s="2">
-        <v>723</v>
+        <v>735</v>
       </c>
       <c r="G89" s="2">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H89" s="2">
-        <v>136</v>
-      </c>
-      <c r="I89" s="2">
-        <v>9559</v>
+        <v>143</v>
+      </c>
+      <c r="I89" s="4">
+        <v>9690</v>
       </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B90" s="2">
         <v>7800</v>
       </c>
       <c r="C90" s="2">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="D90" s="2">
         <v>0</v>
@@ -3341,19 +3359,19 @@
       <c r="H90" s="2">
         <v>0</v>
       </c>
-      <c r="I90" s="2">
-        <v>8137</v>
+      <c r="I90" s="4">
+        <v>8146</v>
       </c>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B91" s="2">
         <v>7000</v>
       </c>
       <c r="C91" s="2">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="D91" s="2">
         <v>0</v>
@@ -3370,22 +3388,22 @@
       <c r="H91" s="2">
         <v>0</v>
       </c>
-      <c r="I91" s="2">
-        <v>8101</v>
+      <c r="I91" s="4">
+        <v>8103</v>
       </c>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B92" s="2">
-        <v>6300</v>
+        <v>0</v>
       </c>
       <c r="C92" s="2">
-        <v>189</v>
+        <v>0</v>
       </c>
       <c r="D92" s="2">
-        <v>0</v>
+        <v>7419</v>
       </c>
       <c r="E92" s="2">
         <v>0</v>
@@ -3394,27 +3412,27 @@
         <v>0</v>
       </c>
       <c r="G92" s="2">
-        <v>921</v>
+        <v>0</v>
       </c>
       <c r="H92" s="2">
         <v>0</v>
       </c>
-      <c r="I92" s="2">
-        <v>7410</v>
+      <c r="I92" s="4">
+        <v>7419</v>
       </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B93" s="2">
-        <v>0</v>
+        <v>6300</v>
       </c>
       <c r="C93" s="2">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="D93" s="2">
-        <v>7366</v>
+        <v>0</v>
       </c>
       <c r="E93" s="2">
         <v>0</v>
@@ -3423,24 +3441,24 @@
         <v>0</v>
       </c>
       <c r="G93" s="2">
-        <v>0</v>
+        <v>914</v>
       </c>
       <c r="H93" s="2">
         <v>0</v>
       </c>
-      <c r="I93" s="2">
-        <v>7366</v>
+      <c r="I93" s="4">
+        <v>7404</v>
       </c>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B94" s="2">
         <v>5900</v>
       </c>
       <c r="C94" s="2">
-        <v>523</v>
+        <v>553</v>
       </c>
       <c r="D94" s="2">
         <v>0</v>
@@ -3457,16 +3475,16 @@
       <c r="H94" s="2">
         <v>0</v>
       </c>
-      <c r="I94" s="2">
-        <v>6423</v>
+      <c r="I94" s="4">
+        <v>6453</v>
       </c>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B95" s="2">
-        <v>5800</v>
+        <v>5700</v>
       </c>
       <c r="C95" s="2">
         <v>0</v>
@@ -3486,13 +3504,13 @@
       <c r="H95" s="2">
         <v>0</v>
       </c>
-      <c r="I95" s="2">
-        <v>5800</v>
+      <c r="I95" s="4">
+        <v>5700</v>
       </c>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B96" s="2">
         <v>1400</v>
@@ -3501,7 +3519,7 @@
         <v>0</v>
       </c>
       <c r="D96" s="2">
-        <v>3728</v>
+        <v>3810</v>
       </c>
       <c r="E96" s="2">
         <v>0</v>
@@ -3513,21 +3531,21 @@
         <v>0</v>
       </c>
       <c r="H96" s="2">
-        <v>416</v>
-      </c>
-      <c r="I96" s="2">
-        <v>5544</v>
+        <v>436</v>
+      </c>
+      <c r="I96" s="4">
+        <v>5646</v>
       </c>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B97" s="2">
-        <v>3500</v>
+        <v>3600</v>
       </c>
       <c r="C97" s="2">
-        <v>434</v>
+        <v>453</v>
       </c>
       <c r="D97" s="2">
         <v>0</v>
@@ -3542,21 +3560,21 @@
         <v>0</v>
       </c>
       <c r="H97" s="2">
-        <v>37</v>
-      </c>
-      <c r="I97" s="2">
-        <v>3971</v>
+        <v>36</v>
+      </c>
+      <c r="I97" s="4">
+        <v>4089</v>
       </c>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B98" s="2">
         <v>2100</v>
       </c>
       <c r="C98" s="2">
-        <v>1313</v>
+        <v>1318</v>
       </c>
       <c r="D98" s="2">
         <v>0</v>
@@ -3573,19 +3591,19 @@
       <c r="H98" s="2">
         <v>0</v>
       </c>
-      <c r="I98" s="2">
-        <v>3413</v>
+      <c r="I98" s="4">
+        <v>3418</v>
       </c>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B99" s="2">
         <v>2400</v>
       </c>
       <c r="C99" s="2">
-        <v>798</v>
+        <v>789</v>
       </c>
       <c r="D99" s="2">
         <v>0</v>
@@ -3602,13 +3620,13 @@
       <c r="H99" s="2">
         <v>0</v>
       </c>
-      <c r="I99" s="2">
-        <v>3198</v>
+      <c r="I99" s="4">
+        <v>3189</v>
       </c>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B100" s="2">
         <v>2500</v>
@@ -3631,13 +3649,13 @@
       <c r="H100" s="2">
         <v>0</v>
       </c>
-      <c r="I100" s="2">
+      <c r="I100" s="4">
         <v>2500</v>
       </c>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B101" s="2">
         <v>2300</v>
@@ -3660,13 +3678,13 @@
       <c r="H101" s="2">
         <v>0</v>
       </c>
-      <c r="I101" s="2">
+      <c r="I101" s="4">
         <v>2300</v>
       </c>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B102" s="2">
         <v>2200</v>
@@ -3689,13 +3707,13 @@
       <c r="H102" s="2">
         <v>0</v>
       </c>
-      <c r="I102" s="2">
+      <c r="I102" s="4">
         <v>2200</v>
       </c>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B103" s="2">
         <v>2100</v>
@@ -3718,13 +3736,13 @@
       <c r="H103" s="2">
         <v>0</v>
       </c>
-      <c r="I103" s="2">
+      <c r="I103" s="4">
         <v>2100</v>
       </c>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B104" s="2">
         <v>1500</v>
@@ -3745,15 +3763,15 @@
         <v>0</v>
       </c>
       <c r="H104" s="2">
-        <v>318</v>
-      </c>
-      <c r="I104" s="2">
-        <v>1818</v>
+        <v>319</v>
+      </c>
+      <c r="I104" s="4">
+        <v>1819</v>
       </c>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B105" s="2">
         <v>1000</v>
@@ -3776,7 +3794,7 @@
       <c r="H105" s="2">
         <v>0</v>
       </c>
-      <c r="I105" s="2">
+      <c r="I105" s="4">
         <v>1000</v>
       </c>
     </row>
